--- a/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV18_current_D1_event_summary_data.xlsx
+++ b/Project 1 Data Quality Assessment/D1 Sensor health/outputs/plot_data/FigV18_current_D1_event_summary_data.xlsx
@@ -448,7 +448,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>d1-final-8fdd3599890f</t>
+          <t>d1-final-33fa914b2f71</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
